--- a/saida/margem-linhas-rodoviarias.xlsx
+++ b/saida/margem-linhas-rodoviarias.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumo'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Linhas'!$A$4:$AD$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Linhas'!$A$4:$AF$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Linhas'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mensal'!$A$4:$AB$484</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mensal'!$1:$1</definedName>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -563,13 +563,15 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="39" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="39" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -834,35 +836,45 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
+          <t>LF de equilibrio</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Folga de ocupacao</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
           <t>Yield (R$/pax-km)</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>RASK</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>CASK total</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>Spread RASK-CASK</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>MC %</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>Classificacao</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="N26" s="13" t="inlineStr">
         <is>
           <t>Alavanca</t>
         </is>
@@ -890,27 +902,33 @@
       <c r="E27" s="16" t="n">
         <v>0.6157236450268017</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="16" t="n">
+        <v>0.8190250439898525</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>-0.2033013989630509</v>
+      </c>
+      <c r="H27" s="17" t="n">
         <v>0.1498863102301447</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="I27" s="17" t="n">
         <v>0.09228854527452268</v>
       </c>
-      <c r="H27" s="17" t="n">
+      <c r="J27" s="17" t="n">
         <v>0.1227606418297209</v>
       </c>
-      <c r="I27" s="17" t="n">
+      <c r="K27" s="17" t="n">
         <v>-0.03047209655519827</v>
       </c>
-      <c r="J27" s="16" t="n">
+      <c r="L27" s="16" t="n">
         <v>-0.0742708795506775</v>
       </c>
-      <c r="K27" s="18" t="inlineStr">
+      <c r="M27" s="18" t="inlineStr">
         <is>
           <t>REVER</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -938,27 +956,33 @@
       <c r="E28" s="21" t="n">
         <v>0.5030077427039905</v>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="21" t="n">
+        <v>0.6616411764710991</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>-0.1586334337671086</v>
+      </c>
+      <c r="H28" s="22" t="n">
         <v>0.1555329570108785</v>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="I28" s="22" t="n">
         <v>0.07823428162211878</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="J28" s="22" t="n">
         <v>0.1029070086567065</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="K28" s="22" t="n">
         <v>-0.02467272703458773</v>
       </c>
-      <c r="J28" s="21" t="n">
+      <c r="L28" s="21" t="n">
         <v>-0.01348490568976509</v>
       </c>
-      <c r="K28" s="18" t="inlineStr">
+      <c r="M28" s="18" t="inlineStr">
         <is>
           <t>REVER</t>
         </is>
       </c>
-      <c r="L28" s="19" t="inlineStr">
+      <c r="N28" s="19" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -986,27 +1010,33 @@
       <c r="E29" s="16" t="n">
         <v>0.5804004214963119</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="16" t="n">
+        <v>0.6305495764948237</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>-0.0501491549985118</v>
+      </c>
+      <c r="H29" s="17" t="n">
         <v>0.3600245203798887</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="I29" s="17" t="n">
         <v>0.2089583833774949</v>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="J29" s="17" t="n">
         <v>0.2270133088532909</v>
       </c>
-      <c r="I29" s="17" t="n">
+      <c r="K29" s="17" t="n">
         <v>-0.01805492547579593</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="L29" s="16" t="n">
         <v>0.1135647946543504</v>
       </c>
-      <c r="K29" s="23" t="inlineStr">
+      <c r="M29" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>ocupacao (rever frequencia e horario)</t>
         </is>
@@ -1034,27 +1064,33 @@
       <c r="E30" s="21" t="n">
         <v>0.5619047619047619</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="21" t="n">
+        <v>0.630994551067821</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>-0.06908978916305908</v>
+      </c>
+      <c r="H30" s="22" t="n">
         <v>0.2196662309207528</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="I30" s="22" t="n">
         <v>0.1234315011840421</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="J30" s="22" t="n">
         <v>0.1386081947646007</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="K30" s="22" t="n">
         <v>-0.01517669358055865</v>
       </c>
-      <c r="J30" s="21" t="n">
+      <c r="L30" s="21" t="n">
         <v>0.08660966205257427</v>
       </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="M30" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="L30" s="19" t="inlineStr">
+      <c r="N30" s="19" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -1082,27 +1118,33 @@
       <c r="E31" s="16" t="n">
         <v>0.5778864970645793</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="16" t="n">
+        <v>0.6432850854079781</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>-0.06539858834339884</v>
+      </c>
+      <c r="H31" s="17" t="n">
         <v>0.2119141472408683</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="I31" s="17" t="n">
         <v>0.1224623242274529</v>
       </c>
-      <c r="H31" s="17" t="n">
+      <c r="J31" s="17" t="n">
         <v>0.1363212103070008</v>
       </c>
-      <c r="I31" s="17" t="n">
+      <c r="K31" s="17" t="n">
         <v>-0.01385888607954795</v>
       </c>
-      <c r="J31" s="16" t="n">
+      <c r="L31" s="16" t="n">
         <v>0.09805601993066369</v>
       </c>
-      <c r="K31" s="23" t="inlineStr">
+      <c r="M31" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="N31" s="14" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -1130,27 +1172,33 @@
       <c r="E32" s="21" t="n">
         <v>0.5962818003913894</v>
       </c>
-      <c r="F32" s="22" t="n">
+      <c r="F32" s="21" t="n">
+        <v>0.6246456579360248</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>-0.02836385754463533</v>
+      </c>
+      <c r="H32" s="22" t="n">
         <v>0.2226417045431627</v>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="I32" s="22" t="n">
         <v>0.1327571964272048</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="J32" s="22" t="n">
         <v>0.1390721740183619</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="K32" s="22" t="n">
         <v>-0.006314977591157067</v>
       </c>
-      <c r="J32" s="21" t="n">
+      <c r="L32" s="21" t="n">
         <v>0.1472769621518367</v>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="M32" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="L32" s="19" t="inlineStr">
+      <c r="N32" s="19" t="inlineStr">
         <is>
           <t>ocupacao (rever frequencia e horario)</t>
         </is>
@@ -1168,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1184,23 +1232,25 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="41" customWidth="1" min="29" max="29"/>
-    <col width="39" customWidth="1" min="30" max="30"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="41" customWidth="1" min="31" max="31"/>
+    <col width="39" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1285,85 +1335,95 @@
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
+          <t>LF de equilibrio</t>
+        </is>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>Folga de ocupacao</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
           <t>Tarifa media</t>
         </is>
       </c>
-      <c r="O4" s="13" t="inlineStr">
+      <c r="Q4" s="13" t="inlineStr">
         <is>
           <t>Yield (R$/pax-km)</t>
         </is>
       </c>
-      <c r="P4" s="13" t="inlineStr">
+      <c r="R4" s="13" t="inlineStr">
         <is>
           <t>RASK</t>
         </is>
       </c>
-      <c r="Q4" s="13" t="inlineStr">
+      <c r="S4" s="13" t="inlineStr">
         <is>
           <t>CASK variavel</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="T4" s="13" t="inlineStr">
         <is>
           <t>CASK total</t>
         </is>
       </c>
-      <c r="S4" s="13" t="inlineStr">
+      <c r="U4" s="13" t="inlineStr">
         <is>
           <t>Spread RASK-CASK</t>
         </is>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="V4" s="13" t="inlineStr">
         <is>
           <t>Receita</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="W4" s="13" t="inlineStr">
         <is>
           <t>Custo variavel</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="X4" s="13" t="inlineStr">
         <is>
           <t>Margem contrib.</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
+      <c r="Y4" s="13" t="inlineStr">
         <is>
           <t>MC %</t>
         </is>
       </c>
-      <c r="X4" s="13" t="inlineStr">
+      <c r="Z4" s="13" t="inlineStr">
         <is>
           <t>Fixo rateado</t>
         </is>
       </c>
-      <c r="Y4" s="13" t="inlineStr">
+      <c r="AA4" s="13" t="inlineStr">
         <is>
           <t>Custo total</t>
         </is>
       </c>
-      <c r="Z4" s="13" t="inlineStr">
+      <c r="AB4" s="13" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
-      <c r="AA4" s="13" t="inlineStr">
+      <c r="AC4" s="13" t="inlineStr">
         <is>
           <t>Classificacao</t>
         </is>
       </c>
-      <c r="AB4" s="13" t="inlineStr">
+      <c r="AD4" s="13" t="inlineStr">
         <is>
           <t>No limite</t>
         </is>
       </c>
-      <c r="AC4" s="13" t="inlineStr">
+      <c r="AE4" s="13" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="AD4" s="13" t="inlineStr">
+      <c r="AF4" s="13" t="inlineStr">
         <is>
           <t>Alavanca</t>
         </is>
@@ -1419,61 +1479,67 @@
       <c r="M5" s="16" t="n">
         <v>0.7344814090019569</v>
       </c>
-      <c r="N5" s="24" t="n">
+      <c r="N5" s="16" t="n">
+        <v>0.4654802770723161</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>0.2690011319296408</v>
+      </c>
+      <c r="P5" s="24" t="n">
         <v>105.3194950087037</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="Q5" s="17" t="n">
         <v>0.2581360171781953</v>
       </c>
-      <c r="P5" s="17" t="n">
+      <c r="R5" s="17" t="n">
         <v>0.1895961056111942</v>
       </c>
-      <c r="Q5" s="17" t="n">
+      <c r="S5" s="17" t="n">
         <v>0.09429017061370001</v>
       </c>
-      <c r="R5" s="17" t="n">
+      <c r="T5" s="17" t="n">
         <v>0.1201572247984505</v>
       </c>
-      <c r="S5" s="17" t="n">
+      <c r="U5" s="17" t="n">
         <v>0.06943888081274376</v>
       </c>
-      <c r="T5" s="25" t="n">
+      <c r="V5" s="25" t="n">
         <v>5929276.93</v>
       </c>
-      <c r="U5" s="25" t="n">
+      <c r="W5" s="25" t="n">
         <v>2948755.363636363</v>
       </c>
-      <c r="V5" s="25" t="n">
+      <c r="X5" s="25" t="n">
         <v>2980521.566363636</v>
       </c>
-      <c r="W5" s="16" t="n">
+      <c r="Y5" s="16" t="n">
         <v>0.5026787585655299</v>
       </c>
-      <c r="X5" s="25" t="n">
+      <c r="Z5" s="25" t="n">
         <v>808945.5589305384</v>
       </c>
-      <c r="Y5" s="25" t="n">
+      <c r="AA5" s="25" t="n">
         <v>3757700.922566902</v>
       </c>
-      <c r="Z5" s="25" t="n">
+      <c r="AB5" s="25" t="n">
         <v>2171576.007433098</v>
       </c>
-      <c r="AA5" s="26" t="inlineStr">
+      <c r="AC5" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB5" s="14" t="inlineStr">
+      <c r="AD5" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC5" s="14" t="inlineStr">
+      <c r="AE5" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD5" s="14" t="inlineStr">
+      <c r="AF5" s="14" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -1529,61 +1595,67 @@
       <c r="M6" s="21" t="n">
         <v>0.7369551681195516</v>
       </c>
-      <c r="N6" s="27" t="n">
+      <c r="N6" s="21" t="n">
+        <v>0.4927041259333277</v>
+      </c>
+      <c r="O6" s="21" t="n">
+        <v>0.2442510421862239</v>
+      </c>
+      <c r="P6" s="27" t="n">
         <v>48.09530086040584</v>
       </c>
-      <c r="O6" s="22" t="n">
+      <c r="Q6" s="22" t="n">
         <v>0.2301210567483533</v>
       </c>
-      <c r="P6" s="22" t="n">
+      <c r="R6" s="22" t="n">
         <v>0.1695889020638316</v>
       </c>
-      <c r="Q6" s="22" t="n">
+      <c r="S6" s="22" t="n">
         <v>0.08869031512951658</v>
       </c>
-      <c r="R6" s="22" t="n">
+      <c r="T6" s="22" t="n">
         <v>0.1133815941240511</v>
       </c>
-      <c r="S6" s="22" t="n">
+      <c r="U6" s="22" t="n">
         <v>0.05620730793978049</v>
       </c>
-      <c r="T6" s="28" t="n">
+      <c r="V6" s="28" t="n">
         <v>3415391.6</v>
       </c>
-      <c r="U6" s="28" t="n">
+      <c r="W6" s="28" t="n">
         <v>1786155.542068966</v>
       </c>
-      <c r="V6" s="28" t="n">
+      <c r="X6" s="28" t="n">
         <v>1629236.057931035</v>
       </c>
-      <c r="W6" s="21" t="n">
+      <c r="Y6" s="21" t="n">
         <v>0.4770275999774183</v>
       </c>
-      <c r="X6" s="28" t="n">
+      <c r="Z6" s="28" t="n">
         <v>497263.5935778898</v>
       </c>
-      <c r="Y6" s="28" t="n">
+      <c r="AA6" s="28" t="n">
         <v>2283419.135646855</v>
       </c>
-      <c r="Z6" s="28" t="n">
+      <c r="AB6" s="28" t="n">
         <v>1131972.464353145</v>
       </c>
-      <c r="AA6" s="26" t="inlineStr">
+      <c r="AC6" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB6" s="19" t="inlineStr">
+      <c r="AD6" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC6" s="19" t="inlineStr">
+      <c r="AE6" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD6" s="19" t="inlineStr">
+      <c r="AF6" s="19" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -1639,61 +1711,67 @@
       <c r="M7" s="16" t="n">
         <v>0.6843226788432268</v>
       </c>
-      <c r="N7" s="24" t="n">
+      <c r="N7" s="16" t="n">
+        <v>0.4680925825253062</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>0.2162300963179207</v>
+      </c>
+      <c r="P7" s="24" t="n">
         <v>120.7216023767158</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="Q7" s="17" t="n">
         <v>0.2536168117157895</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="R7" s="17" t="n">
         <v>0.1735557359930273</v>
       </c>
-      <c r="Q7" s="17" t="n">
+      <c r="S7" s="17" t="n">
         <v>0.0928490941831278</v>
       </c>
-      <c r="R7" s="17" t="n">
+      <c r="T7" s="17" t="n">
         <v>0.1187161483678782</v>
       </c>
-      <c r="S7" s="17" t="n">
+      <c r="U7" s="17" t="n">
         <v>0.05483958762514909</v>
       </c>
-      <c r="T7" s="25" t="n">
+      <c r="V7" s="25" t="n">
         <v>3799350.27</v>
       </c>
-      <c r="U7" s="25" t="n">
+      <c r="W7" s="25" t="n">
         <v>2032581.804545454</v>
       </c>
-      <c r="V7" s="25" t="n">
+      <c r="X7" s="25" t="n">
         <v>1766768.465454546</v>
       </c>
-      <c r="W7" s="16" t="n">
+      <c r="Y7" s="16" t="n">
         <v>0.4650185794674165</v>
       </c>
-      <c r="X7" s="25" t="n">
+      <c r="Z7" s="25" t="n">
         <v>566261.8912513768</v>
       </c>
-      <c r="Y7" s="25" t="n">
+      <c r="AA7" s="25" t="n">
         <v>2598843.695796831</v>
       </c>
-      <c r="Z7" s="25" t="n">
+      <c r="AB7" s="25" t="n">
         <v>1200506.574203169</v>
       </c>
-      <c r="AA7" s="26" t="inlineStr">
+      <c r="AC7" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB7" s="14" t="inlineStr">
+      <c r="AD7" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC7" s="14" t="inlineStr">
+      <c r="AE7" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD7" s="14" t="inlineStr">
+      <c r="AF7" s="14" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -1749,61 +1827,67 @@
       <c r="M8" s="21" t="n">
         <v>0.7294455316373124</v>
       </c>
-      <c r="N8" s="27" t="n">
+      <c r="N8" s="21" t="n">
+        <v>0.5024576452691002</v>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>0.2269878863682122</v>
+      </c>
+      <c r="P8" s="27" t="n">
         <v>138.9413025826298</v>
       </c>
-      <c r="O8" s="22" t="n">
+      <c r="Q8" s="22" t="n">
         <v>0.2371011989464673</v>
       </c>
-      <c r="P8" s="22" t="n">
+      <c r="R8" s="22" t="n">
         <v>0.17295241011735</v>
       </c>
-      <c r="Q8" s="22" t="n">
+      <c r="S8" s="22" t="n">
         <v>0.09326625592837197</v>
       </c>
-      <c r="R8" s="22" t="n">
+      <c r="T8" s="22" t="n">
         <v>0.1191333101131224</v>
       </c>
-      <c r="S8" s="22" t="n">
+      <c r="U8" s="22" t="n">
         <v>0.05381910000422759</v>
       </c>
-      <c r="T8" s="28" t="n">
+      <c r="V8" s="28" t="n">
         <v>7768486.109999999</v>
       </c>
-      <c r="U8" s="28" t="n">
+      <c r="W8" s="28" t="n">
         <v>4189231.090909091</v>
       </c>
-      <c r="V8" s="28" t="n">
+      <c r="X8" s="28" t="n">
         <v>3579255.019090909</v>
       </c>
-      <c r="W8" s="21" t="n">
+      <c r="Y8" s="21" t="n">
         <v>0.460740351261426</v>
       </c>
-      <c r="X8" s="28" t="n">
+      <c r="Z8" s="28" t="n">
         <v>1161867.886111018</v>
       </c>
-      <c r="Y8" s="28" t="n">
+      <c r="AA8" s="28" t="n">
         <v>5351098.977020109</v>
       </c>
-      <c r="Z8" s="28" t="n">
+      <c r="AB8" s="28" t="n">
         <v>2417387.13297989</v>
       </c>
-      <c r="AA8" s="26" t="inlineStr">
+      <c r="AC8" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB8" s="19" t="inlineStr">
+      <c r="AD8" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC8" s="19" t="inlineStr">
+      <c r="AE8" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD8" s="19" t="inlineStr">
+      <c r="AF8" s="19" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -1859,61 +1943,67 @@
       <c r="M9" s="16" t="n">
         <v>0.7096720630967206</v>
       </c>
-      <c r="N9" s="24" t="n">
+      <c r="N9" s="16" t="n">
+        <v>0.4884459576720895</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>0.2212261054246311</v>
+      </c>
+      <c r="P9" s="24" t="n">
         <v>68.98649947356107</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="Q9" s="17" t="n">
         <v>0.2299549982452036</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="R9" s="17" t="n">
         <v>0.1631926380240764</v>
       </c>
-      <c r="Q9" s="17" t="n">
+      <c r="S9" s="17" t="n">
         <v>0.08762931034482759</v>
       </c>
-      <c r="R9" s="17" t="n">
+      <c r="T9" s="17" t="n">
         <v>0.1123205893393621</v>
       </c>
-      <c r="S9" s="17" t="n">
+      <c r="U9" s="17" t="n">
         <v>0.05087204868471426</v>
       </c>
-      <c r="T9" s="25" t="n">
+      <c r="V9" s="25" t="n">
         <v>2358786.39</v>
       </c>
-      <c r="U9" s="25" t="n">
+      <c r="W9" s="25" t="n">
         <v>1266594.051724138</v>
       </c>
-      <c r="V9" s="25" t="n">
+      <c r="X9" s="25" t="n">
         <v>1092192.338275862</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="Y9" s="16" t="n">
         <v>0.463031473687561</v>
       </c>
-      <c r="X9" s="25" t="n">
+      <c r="Z9" s="25" t="n">
         <v>356887.7465870022</v>
       </c>
-      <c r="Y9" s="25" t="n">
+      <c r="AA9" s="25" t="n">
         <v>1623481.79831114</v>
       </c>
-      <c r="Z9" s="25" t="n">
+      <c r="AB9" s="25" t="n">
         <v>735304.59168886</v>
       </c>
-      <c r="AA9" s="26" t="inlineStr">
+      <c r="AC9" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB9" s="14" t="inlineStr">
+      <c r="AD9" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC9" s="14" t="inlineStr">
+      <c r="AE9" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD9" s="14" t="inlineStr">
+      <c r="AF9" s="14" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -1969,61 +2059,67 @@
       <c r="M10" s="21" t="n">
         <v>0.6615133724722766</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N10" s="21" t="n">
+        <v>0.4916924176006658</v>
+      </c>
+      <c r="O10" s="21" t="n">
+        <v>0.1698209548716108</v>
+      </c>
+      <c r="P10" s="27" t="n">
         <v>105.8746718765408</v>
       </c>
-      <c r="O10" s="22" t="n">
+      <c r="Q10" s="22" t="n">
         <v>0.2439508568583889</v>
       </c>
-      <c r="P10" s="22" t="n">
+      <c r="R10" s="22" t="n">
         <v>0.1613767540378944</v>
       </c>
-      <c r="Q10" s="22" t="n">
+      <c r="S10" s="22" t="n">
         <v>0.09408173239970474</v>
       </c>
-      <c r="R10" s="22" t="n">
+      <c r="T10" s="22" t="n">
         <v>0.1199487865844552</v>
       </c>
-      <c r="S10" s="22" t="n">
+      <c r="U10" s="22" t="n">
         <v>0.04142796745343923</v>
       </c>
-      <c r="T10" s="28" t="n">
+      <c r="V10" s="28" t="n">
         <v>4294700.19</v>
       </c>
-      <c r="U10" s="28" t="n">
+      <c r="W10" s="28" t="n">
         <v>2503785.854545454</v>
       </c>
-      <c r="V10" s="28" t="n">
+      <c r="X10" s="28" t="n">
         <v>1790914.335454546</v>
       </c>
-      <c r="W10" s="21" t="n">
+      <c r="Y10" s="21" t="n">
         <v>0.4170056712281343</v>
       </c>
-      <c r="X10" s="28" t="n">
+      <c r="Z10" s="28" t="n">
         <v>688396.8089722621</v>
       </c>
-      <c r="Y10" s="28" t="n">
+      <c r="AA10" s="28" t="n">
         <v>3192182.663517717</v>
       </c>
-      <c r="Z10" s="28" t="n">
+      <c r="AB10" s="28" t="n">
         <v>1102517.526482284</v>
       </c>
-      <c r="AA10" s="26" t="inlineStr">
+      <c r="AC10" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB10" s="19" t="inlineStr">
+      <c r="AD10" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC10" s="19" t="inlineStr">
+      <c r="AE10" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD10" s="19" t="inlineStr">
+      <c r="AF10" s="19" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2079,61 +2175,67 @@
       <c r="M11" s="16" t="n">
         <v>0.7083085169743896</v>
       </c>
-      <c r="N11" s="24" t="n">
+      <c r="N11" s="16" t="n">
+        <v>0.533390173295604</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>0.1749183436787856</v>
+      </c>
+      <c r="P11" s="24" t="n">
         <v>51.10262707588816</v>
       </c>
-      <c r="O11" s="17" t="n">
+      <c r="Q11" s="17" t="n">
         <v>0.1980721979685588</v>
       </c>
-      <c r="P11" s="17" t="n">
+      <c r="R11" s="17" t="n">
         <v>0.1402962247969675</v>
       </c>
-      <c r="Q11" s="17" t="n">
+      <c r="S11" s="17" t="n">
         <v>0.08203201887428378</v>
       </c>
-      <c r="R11" s="17" t="n">
+      <c r="T11" s="17" t="n">
         <v>0.1056497639994907</v>
       </c>
-      <c r="S11" s="17" t="n">
+      <c r="U11" s="17" t="n">
         <v>0.0346464607974768</v>
       </c>
-      <c r="T11" s="25" t="n">
+      <c r="V11" s="25" t="n">
         <v>2430951.97</v>
       </c>
-      <c r="U11" s="25" t="n">
+      <c r="W11" s="25" t="n">
         <v>1421391.76</v>
       </c>
-      <c r="V11" s="25" t="n">
+      <c r="X11" s="25" t="n">
         <v>1009560.21</v>
       </c>
-      <c r="W11" s="16" t="n">
+      <c r="Y11" s="16" t="n">
         <v>0.4152941820565874</v>
       </c>
-      <c r="X11" s="25" t="n">
+      <c r="Z11" s="25" t="n">
         <v>409231.2827530959</v>
       </c>
-      <c r="Y11" s="25" t="n">
+      <c r="AA11" s="25" t="n">
         <v>1830623.042753096</v>
       </c>
-      <c r="Z11" s="25" t="n">
+      <c r="AB11" s="25" t="n">
         <v>600328.9272469038</v>
       </c>
-      <c r="AA11" s="26" t="inlineStr">
+      <c r="AC11" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB11" s="14" t="inlineStr">
+      <c r="AD11" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC11" s="14" t="inlineStr">
+      <c r="AE11" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD11" s="14" t="inlineStr">
+      <c r="AF11" s="14" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2189,61 +2291,67 @@
       <c r="M12" s="21" t="n">
         <v>0.7574897705034691</v>
       </c>
-      <c r="N12" s="27" t="n">
+      <c r="N12" s="21" t="n">
+        <v>0.5800877327557055</v>
+      </c>
+      <c r="O12" s="21" t="n">
+        <v>0.1774020377477636</v>
+      </c>
+      <c r="P12" s="27" t="n">
         <v>82.76112721209061</v>
       </c>
-      <c r="O12" s="22" t="n">
+      <c r="Q12" s="22" t="n">
         <v>0.1929163804477637</v>
       </c>
-      <c r="P12" s="22" t="n">
+      <c r="R12" s="22" t="n">
         <v>0.1461321847517364</v>
       </c>
-      <c r="Q12" s="22" t="n">
+      <c r="S12" s="22" t="n">
         <v>0.0872171467508458</v>
       </c>
-      <c r="R12" s="22" t="n">
+      <c r="T12" s="22" t="n">
         <v>0.1119084257453803</v>
       </c>
-      <c r="S12" s="22" t="n">
+      <c r="U12" s="22" t="n">
         <v>0.0342237590063561</v>
       </c>
-      <c r="T12" s="28" t="n">
+      <c r="V12" s="28" t="n">
         <v>7047689.310000001</v>
       </c>
-      <c r="U12" s="28" t="n">
+      <c r="W12" s="28" t="n">
         <v>4206324.252586206</v>
       </c>
-      <c r="V12" s="28" t="n">
+      <c r="X12" s="28" t="n">
         <v>2841365.057413794</v>
       </c>
-      <c r="W12" s="21" t="n">
+      <c r="Y12" s="21" t="n">
         <v>0.4031626441565986</v>
       </c>
-      <c r="X12" s="28" t="n">
+      <c r="Z12" s="28" t="n">
         <v>1190815.447778631</v>
       </c>
-      <c r="Y12" s="28" t="n">
+      <c r="AA12" s="28" t="n">
         <v>5397139.700364837</v>
       </c>
-      <c r="Z12" s="28" t="n">
+      <c r="AB12" s="28" t="n">
         <v>1650549.609635163</v>
       </c>
-      <c r="AA12" s="26" t="inlineStr">
+      <c r="AC12" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB12" s="19" t="inlineStr">
+      <c r="AD12" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC12" s="19" t="inlineStr">
+      <c r="AE12" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD12" s="19" t="inlineStr">
+      <c r="AF12" s="19" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2299,61 +2407,67 @@
       <c r="M13" s="16" t="n">
         <v>0.6502283105022831</v>
       </c>
-      <c r="N13" s="24" t="n">
+      <c r="N13" s="16" t="n">
+        <v>0.5123444566946136</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>0.1378838538076695</v>
+      </c>
+      <c r="P13" s="24" t="n">
         <v>76.88150248978549</v>
       </c>
-      <c r="O13" s="17" t="n">
+      <c r="Q13" s="17" t="n">
         <v>0.2159592766567008</v>
       </c>
-      <c r="P13" s="17" t="n">
+      <c r="R13" s="17" t="n">
         <v>0.1404228355977817</v>
       </c>
-      <c r="Q13" s="17" t="n">
+      <c r="S13" s="17" t="n">
         <v>0.08595425927230461</v>
       </c>
-      <c r="R13" s="17" t="n">
+      <c r="T13" s="17" t="n">
         <v>0.1106455382668391</v>
       </c>
-      <c r="S13" s="17" t="n">
+      <c r="U13" s="17" t="n">
         <v>0.02977729733094259</v>
       </c>
-      <c r="T13" s="25" t="n">
+      <c r="V13" s="25" t="n">
         <v>2408543.71</v>
       </c>
-      <c r="U13" s="25" t="n">
+      <c r="W13" s="25" t="n">
         <v>1474294.33137931</v>
       </c>
-      <c r="V13" s="25" t="n">
+      <c r="X13" s="25" t="n">
         <v>934249.3786206895</v>
       </c>
-      <c r="W13" s="16" t="n">
+      <c r="Y13" s="16" t="n">
         <v>0.3878897338428164</v>
       </c>
-      <c r="X13" s="25" t="n">
+      <c r="Z13" s="25" t="n">
         <v>423506.792616576</v>
       </c>
-      <c r="Y13" s="25" t="n">
+      <c r="AA13" s="25" t="n">
         <v>1897801.123995886</v>
       </c>
-      <c r="Z13" s="25" t="n">
+      <c r="AB13" s="25" t="n">
         <v>510742.5860041135</v>
       </c>
-      <c r="AA13" s="26" t="inlineStr">
+      <c r="AC13" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB13" s="14" t="inlineStr">
+      <c r="AD13" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC13" s="14" t="inlineStr">
+      <c r="AE13" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD13" s="14" t="inlineStr">
+      <c r="AF13" s="14" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2409,61 +2523,67 @@
       <c r="M14" s="21" t="n">
         <v>0.698272104607721</v>
       </c>
-      <c r="N14" s="27" t="n">
+      <c r="N14" s="21" t="n">
+        <v>0.569847735903805</v>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>0.128424368703916</v>
+      </c>
+      <c r="P14" s="27" t="n">
         <v>114.6158760059745</v>
       </c>
-      <c r="O14" s="22" t="n">
+      <c r="Q14" s="22" t="n">
         <v>0.1949249591938342</v>
       </c>
-      <c r="P14" s="22" t="n">
+      <c r="R14" s="22" t="n">
         <v>0.1361106614968528</v>
       </c>
-      <c r="Q14" s="22" t="n">
+      <c r="S14" s="22" t="n">
         <v>0.08638626767321349</v>
       </c>
-      <c r="R14" s="22" t="n">
+      <c r="T14" s="22" t="n">
         <v>0.111077546667748</v>
       </c>
-      <c r="S14" s="22" t="n">
+      <c r="U14" s="22" t="n">
         <v>0.02503311482910475</v>
       </c>
-      <c r="T14" s="28" t="n">
+      <c r="V14" s="28" t="n">
         <v>5141324.35</v>
       </c>
-      <c r="U14" s="28" t="n">
+      <c r="W14" s="28" t="n">
         <v>3263078.855172414</v>
       </c>
-      <c r="V14" s="28" t="n">
+      <c r="X14" s="28" t="n">
         <v>1878245.494827586</v>
       </c>
-      <c r="W14" s="21" t="n">
+      <c r="Y14" s="21" t="n">
         <v>0.3653232838398118</v>
       </c>
-      <c r="X14" s="28" t="n">
+      <c r="Z14" s="28" t="n">
         <v>932666.6444140326</v>
       </c>
-      <c r="Y14" s="28" t="n">
+      <c r="AA14" s="28" t="n">
         <v>4195745.499586446</v>
       </c>
-      <c r="Z14" s="28" t="n">
+      <c r="AB14" s="28" t="n">
         <v>945578.8504135534</v>
       </c>
-      <c r="AA14" s="26" t="inlineStr">
+      <c r="AC14" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB14" s="19" t="inlineStr">
+      <c r="AD14" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC14" s="19" t="inlineStr">
+      <c r="AE14" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD14" s="19" t="inlineStr">
+      <c r="AF14" s="19" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2519,61 +2639,67 @@
       <c r="M15" s="16" t="n">
         <v>0.6680464562239429</v>
       </c>
-      <c r="N15" s="24" t="n">
+      <c r="N15" s="16" t="n">
+        <v>0.5908857824588694</v>
+      </c>
+      <c r="O15" s="16" t="n">
+        <v>0.07716067376507352</v>
+      </c>
+      <c r="P15" s="24" t="n">
         <v>93.70749208754958</v>
       </c>
-      <c r="O15" s="17" t="n">
+      <c r="Q15" s="17" t="n">
         <v>0.1745018474628484</v>
       </c>
-      <c r="P15" s="17" t="n">
+      <c r="R15" s="17" t="n">
         <v>0.1165753408020869</v>
       </c>
-      <c r="Q15" s="17" t="n">
+      <c r="S15" s="17" t="n">
         <v>0.07949291555339649</v>
       </c>
-      <c r="R15" s="17" t="n">
+      <c r="T15" s="17" t="n">
         <v>0.1031106606786034</v>
       </c>
-      <c r="S15" s="17" t="n">
+      <c r="U15" s="17" t="n">
         <v>0.01346468012348345</v>
       </c>
-      <c r="T15" s="25" t="n">
+      <c r="V15" s="25" t="n">
         <v>2102140.17</v>
       </c>
-      <c r="U15" s="25" t="n">
+      <c r="W15" s="25" t="n">
         <v>1433452.82</v>
       </c>
-      <c r="V15" s="25" t="n">
+      <c r="X15" s="25" t="n">
         <v>668687.3499999999</v>
       </c>
-      <c r="W15" s="16" t="n">
+      <c r="Y15" s="16" t="n">
         <v>0.3180983644872739</v>
       </c>
-      <c r="X15" s="25" t="n">
+      <c r="Z15" s="25" t="n">
         <v>425886.0442604893</v>
       </c>
-      <c r="Y15" s="25" t="n">
+      <c r="AA15" s="25" t="n">
         <v>1859338.864260489</v>
       </c>
-      <c r="Z15" s="25" t="n">
+      <c r="AB15" s="25" t="n">
         <v>242801.3057395106</v>
       </c>
-      <c r="AA15" s="26" t="inlineStr">
+      <c r="AC15" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB15" s="14" t="inlineStr">
+      <c r="AD15" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC15" s="14" t="inlineStr">
+      <c r="AE15" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD15" s="14" t="inlineStr">
+      <c r="AF15" s="14" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2629,61 +2755,67 @@
       <c r="M16" s="21" t="n">
         <v>0.6357409713574097</v>
       </c>
-      <c r="N16" s="27" t="n">
+      <c r="N16" s="21" t="n">
+        <v>0.572948646637657</v>
+      </c>
+      <c r="O16" s="21" t="n">
+        <v>0.06279232471975271</v>
+      </c>
+      <c r="P16" s="27" t="n">
         <v>101.2643186418544</v>
       </c>
-      <c r="O16" s="22" t="n">
+      <c r="Q16" s="22" t="n">
         <v>0.1943652948979931</v>
       </c>
-      <c r="P16" s="22" t="n">
+      <c r="R16" s="22" t="n">
         <v>0.1235659813766195</v>
       </c>
-      <c r="Q16" s="22" t="n">
+      <c r="S16" s="22" t="n">
         <v>0.0866700536705997</v>
       </c>
-      <c r="R16" s="22" t="n">
+      <c r="T16" s="22" t="n">
         <v>0.1113613326651342</v>
       </c>
-      <c r="S16" s="22" t="n">
+      <c r="U16" s="22" t="n">
         <v>0.01220464871148527</v>
       </c>
-      <c r="T16" s="28" t="n">
+      <c r="V16" s="28" t="n">
         <v>3101726.08</v>
       </c>
-      <c r="U16" s="28" t="n">
+      <c r="W16" s="28" t="n">
         <v>2175572.619827586</v>
       </c>
-      <c r="V16" s="28" t="n">
+      <c r="X16" s="28" t="n">
         <v>926153.4601724138</v>
       </c>
-      <c r="W16" s="21" t="n">
+      <c r="Y16" s="21" t="n">
         <v>0.298592924160606</v>
       </c>
-      <c r="X16" s="28" t="n">
+      <c r="Z16" s="28" t="n">
         <v>619795.0532394273</v>
       </c>
-      <c r="Y16" s="28" t="n">
+      <c r="AA16" s="28" t="n">
         <v>2795367.673067013</v>
       </c>
-      <c r="Z16" s="28" t="n">
+      <c r="AB16" s="28" t="n">
         <v>306358.4069329868</v>
       </c>
-      <c r="AA16" s="26" t="inlineStr">
+      <c r="AC16" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB16" s="19" t="inlineStr">
+      <c r="AD16" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC16" s="19" t="inlineStr">
+      <c r="AE16" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio com folga</t>
         </is>
       </c>
-      <c r="AD16" s="19" t="inlineStr">
+      <c r="AF16" s="19" t="inlineStr">
         <is>
           <t>acompanhar</t>
         </is>
@@ -2739,61 +2871,67 @@
       <c r="M17" s="16" t="n">
         <v>0.6609062170706006</v>
       </c>
-      <c r="N17" s="24" t="n">
+      <c r="N17" s="16" t="n">
+        <v>0.6397558089902593</v>
+      </c>
+      <c r="O17" s="16" t="n">
+        <v>0.0211504080803413</v>
+      </c>
+      <c r="P17" s="24" t="n">
         <v>357.8761814413265</v>
       </c>
-      <c r="O17" s="17" t="n">
+      <c r="Q17" s="17" t="n">
         <v>0.352935090178823</v>
       </c>
-      <c r="P17" s="17" t="n">
+      <c r="R17" s="17" t="n">
         <v>0.2332569953215572</v>
       </c>
-      <c r="Q17" s="17" t="n">
+      <c r="S17" s="17" t="n">
         <v>0.1840070327630369</v>
       </c>
-      <c r="R17" s="17" t="n">
+      <c r="T17" s="17" t="n">
         <v>0.2257922741384031</v>
       </c>
-      <c r="S17" s="17" t="n">
+      <c r="U17" s="17" t="n">
         <v>0.007464721183154166</v>
       </c>
-      <c r="T17" s="25" t="n">
+      <c r="V17" s="25" t="n">
         <v>4489198.82</v>
       </c>
-      <c r="U17" s="25" t="n">
+      <c r="W17" s="25" t="n">
         <v>3541347.830588235</v>
       </c>
-      <c r="V17" s="25" t="n">
+      <c r="X17" s="25" t="n">
         <v>947850.9894117652</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="Y17" s="16" t="n">
         <v>0.2111403453972585</v>
       </c>
-      <c r="X17" s="25" t="n">
+      <c r="Z17" s="25" t="n">
         <v>804187.0556427117</v>
       </c>
-      <c r="Y17" s="25" t="n">
+      <c r="AA17" s="25" t="n">
         <v>4345534.886230947</v>
       </c>
-      <c r="Z17" s="25" t="n">
+      <c r="AB17" s="25" t="n">
         <v>143663.9337690538</v>
       </c>
-      <c r="AA17" s="26" t="inlineStr">
+      <c r="AC17" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB17" s="14" t="inlineStr">
+      <c r="AD17" s="14" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="AC17" s="14" t="inlineStr">
+      <c r="AE17" s="14" t="inlineStr">
         <is>
           <t>cobre o custo cheio, com folga estreita</t>
         </is>
       </c>
-      <c r="AD17" s="14" t="inlineStr">
+      <c r="AF17" s="14" t="inlineStr">
         <is>
           <t>ocupacao (rever frequencia e horario)</t>
         </is>
@@ -2849,61 +2987,67 @@
       <c r="M18" s="21" t="n">
         <v>0.6057729941291585</v>
       </c>
-      <c r="N18" s="27" t="n">
+      <c r="N18" s="21" t="n">
+        <v>0.6021696460216566</v>
+      </c>
+      <c r="O18" s="21" t="n">
+        <v>0.003603348107501958</v>
+      </c>
+      <c r="P18" s="27" t="n">
         <v>160.729158455823</v>
       </c>
-      <c r="O18" s="22" t="n">
+      <c r="Q18" s="22" t="n">
         <v>0.2315982110314452</v>
       </c>
-      <c r="P18" s="22" t="n">
+      <c r="R18" s="22" t="n">
         <v>0.1402959417314753</v>
       </c>
-      <c r="Q18" s="22" t="n">
+      <c r="S18" s="22" t="n">
         <v>0.1135943585713038</v>
       </c>
-      <c r="R18" s="22" t="n">
+      <c r="T18" s="22" t="n">
         <v>0.1394614127560543</v>
       </c>
-      <c r="S18" s="22" t="n">
+      <c r="U18" s="22" t="n">
         <v>0.000834528975420995</v>
       </c>
-      <c r="T18" s="28" t="n">
+      <c r="V18" s="28" t="n">
         <v>2985222.66</v>
       </c>
-      <c r="U18" s="28" t="n">
+      <c r="W18" s="28" t="n">
         <v>2417065.305454546</v>
       </c>
-      <c r="V18" s="28" t="n">
+      <c r="X18" s="28" t="n">
         <v>568157.3545454545</v>
       </c>
-      <c r="W18" s="21" t="n">
+      <c r="Y18" s="21" t="n">
         <v>0.190323275432143</v>
       </c>
-      <c r="X18" s="28" t="n">
+      <c r="Z18" s="28" t="n">
         <v>550400.2136252879</v>
       </c>
-      <c r="Y18" s="28" t="n">
+      <c r="AA18" s="28" t="n">
         <v>2967465.519079833</v>
       </c>
-      <c r="Z18" s="28" t="n">
+      <c r="AB18" s="28" t="n">
         <v>17757.14092016686</v>
       </c>
-      <c r="AA18" s="26" t="inlineStr">
+      <c r="AC18" s="26" t="inlineStr">
         <is>
           <t>MANTER</t>
         </is>
       </c>
-      <c r="AB18" s="19" t="inlineStr">
+      <c r="AD18" s="19" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="AC18" s="19" t="inlineStr">
+      <c r="AE18" s="19" t="inlineStr">
         <is>
           <t>cobre o custo cheio, com folga estreita</t>
         </is>
       </c>
-      <c r="AD18" s="19" t="inlineStr">
+      <c r="AF18" s="19" t="inlineStr">
         <is>
           <t>ocupacao (rever frequencia e horario)</t>
         </is>
@@ -2959,61 +3103,67 @@
       <c r="M19" s="16" t="n">
         <v>0.5962818003913894</v>
       </c>
-      <c r="N19" s="24" t="n">
+      <c r="N19" s="16" t="n">
+        <v>0.6246456579360248</v>
+      </c>
+      <c r="O19" s="16" t="n">
+        <v>-0.02836385754463533</v>
+      </c>
+      <c r="P19" s="24" t="n">
         <v>159.4114604529045</v>
       </c>
-      <c r="O19" s="17" t="n">
+      <c r="Q19" s="17" t="n">
         <v>0.2226417045431627</v>
       </c>
-      <c r="P19" s="17" t="n">
+      <c r="R19" s="17" t="n">
         <v>0.1327571964272048</v>
       </c>
-      <c r="Q19" s="17" t="n">
+      <c r="S19" s="17" t="n">
         <v>0.1132051198336115</v>
       </c>
-      <c r="R19" s="17" t="n">
+      <c r="T19" s="17" t="n">
         <v>0.1390721740183619</v>
       </c>
-      <c r="S19" s="17" t="n">
+      <c r="U19" s="17" t="n">
         <v>-0.006314977591157067</v>
       </c>
-      <c r="T19" s="25" t="n">
+      <c r="V19" s="25" t="n">
         <v>2914360.32</v>
       </c>
-      <c r="U19" s="25" t="n">
+      <c r="W19" s="25" t="n">
         <v>2485142.185454546</v>
       </c>
-      <c r="V19" s="25" t="n">
+      <c r="X19" s="25" t="n">
         <v>429218.1345454548</v>
       </c>
-      <c r="W19" s="16" t="n">
+      <c r="Y19" s="16" t="n">
         <v>0.1472769621518367</v>
       </c>
-      <c r="X19" s="25" t="n">
+      <c r="Z19" s="25" t="n">
         <v>567848.0590139858</v>
       </c>
-      <c r="Y19" s="25" t="n">
+      <c r="AA19" s="25" t="n">
         <v>3052990.244468531</v>
       </c>
-      <c r="Z19" s="25" t="n">
+      <c r="AB19" s="25" t="n">
         <v>-138629.9244685308</v>
       </c>
-      <c r="AA19" s="23" t="inlineStr">
+      <c r="AC19" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="AB19" s="14" t="inlineStr">
+      <c r="AD19" s="14" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="AC19" s="14" t="inlineStr">
+      <c r="AE19" s="14" t="inlineStr">
         <is>
           <t>cobre o variavel, nao o fixo rateado</t>
         </is>
       </c>
-      <c r="AD19" s="14" t="inlineStr">
+      <c r="AF19" s="14" t="inlineStr">
         <is>
           <t>ocupacao (rever frequencia e horario)</t>
         </is>
@@ -3069,61 +3219,67 @@
       <c r="M20" s="21" t="n">
         <v>0.5778864970645793</v>
       </c>
-      <c r="N20" s="27" t="n">
+      <c r="N20" s="21" t="n">
+        <v>0.6432850854079781</v>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>-0.06539858834339884</v>
+      </c>
+      <c r="P20" s="27" t="n">
         <v>197.927813522971</v>
       </c>
-      <c r="O20" s="22" t="n">
+      <c r="Q20" s="22" t="n">
         <v>0.2119141472408683</v>
       </c>
-      <c r="P20" s="22" t="n">
+      <c r="R20" s="22" t="n">
         <v>0.1224623242274529</v>
       </c>
-      <c r="Q20" s="22" t="n">
+      <c r="S20" s="22" t="n">
         <v>0.1104541561222503</v>
       </c>
-      <c r="R20" s="22" t="n">
+      <c r="T20" s="22" t="n">
         <v>0.1363212103070008</v>
       </c>
-      <c r="S20" s="22" t="n">
+      <c r="U20" s="22" t="n">
         <v>-0.01385888607954795</v>
       </c>
-      <c r="T20" s="28" t="n">
+      <c r="V20" s="28" t="n">
         <v>1753442.5</v>
       </c>
-      <c r="U20" s="28" t="n">
+      <c r="W20" s="28" t="n">
         <v>1581506.907272727</v>
       </c>
-      <c r="V20" s="28" t="n">
+      <c r="X20" s="28" t="n">
         <v>171935.5927272728</v>
       </c>
-      <c r="W20" s="21" t="n">
+      <c r="Y20" s="21" t="n">
         <v>0.09805601993066369</v>
       </c>
-      <c r="X20" s="28" t="n">
+      <c r="Z20" s="28" t="n">
         <v>370370.1725691779</v>
       </c>
-      <c r="Y20" s="28" t="n">
+      <c r="AA20" s="28" t="n">
         <v>1951877.079841905</v>
       </c>
-      <c r="Z20" s="28" t="n">
+      <c r="AB20" s="28" t="n">
         <v>-198434.5798419053</v>
       </c>
-      <c r="AA20" s="23" t="inlineStr">
+      <c r="AC20" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="AB20" s="19" t="inlineStr">
+      <c r="AD20" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC20" s="19" t="inlineStr">
+      <c r="AE20" s="19" t="inlineStr">
         <is>
           <t>cobre o variavel, nao o fixo rateado</t>
         </is>
       </c>
-      <c r="AD20" s="19" t="inlineStr">
+      <c r="AF20" s="19" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -3179,61 +3335,67 @@
       <c r="M21" s="16" t="n">
         <v>0.5619047619047619</v>
       </c>
-      <c r="N21" s="24" t="n">
+      <c r="N21" s="16" t="n">
+        <v>0.630994551067821</v>
+      </c>
+      <c r="O21" s="16" t="n">
+        <v>-0.06908978916305908</v>
+      </c>
+      <c r="P21" s="24" t="n">
         <v>177.0509821221268</v>
       </c>
-      <c r="O21" s="17" t="n">
+      <c r="Q21" s="17" t="n">
         <v>0.2196662309207528</v>
       </c>
-      <c r="P21" s="17" t="n">
+      <c r="R21" s="17" t="n">
         <v>0.1234315011840421</v>
       </c>
-      <c r="Q21" s="17" t="n">
+      <c r="S21" s="17" t="n">
         <v>0.1127411405798503</v>
       </c>
-      <c r="R21" s="17" t="n">
+      <c r="T21" s="17" t="n">
         <v>0.1386081947646007</v>
       </c>
-      <c r="S21" s="17" t="n">
+      <c r="U21" s="17" t="n">
         <v>-0.01517669358055865</v>
       </c>
-      <c r="T21" s="25" t="n">
+      <c r="V21" s="25" t="n">
         <v>1525117.16</v>
       </c>
-      <c r="U21" s="25" t="n">
+      <c r="W21" s="25" t="n">
         <v>1393027.278181818</v>
       </c>
-      <c r="V21" s="25" t="n">
+      <c r="X21" s="25" t="n">
         <v>132089.8818181818</v>
       </c>
-      <c r="W21" s="16" t="n">
+      <c r="Y21" s="16" t="n">
         <v>0.08660966205257427</v>
       </c>
-      <c r="X21" s="25" t="n">
+      <c r="Z21" s="25" t="n">
         <v>319612.8041656931</v>
       </c>
-      <c r="Y21" s="25" t="n">
+      <c r="AA21" s="25" t="n">
         <v>1712640.082347511</v>
       </c>
-      <c r="Z21" s="25" t="n">
+      <c r="AB21" s="25" t="n">
         <v>-187522.9223475112</v>
       </c>
-      <c r="AA21" s="23" t="inlineStr">
+      <c r="AC21" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="AB21" s="14" t="inlineStr">
+      <c r="AD21" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC21" s="14" t="inlineStr">
+      <c r="AE21" s="14" t="inlineStr">
         <is>
           <t>cobre o variavel, nao o fixo rateado</t>
         </is>
       </c>
-      <c r="AD21" s="14" t="inlineStr">
+      <c r="AF21" s="14" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -3289,61 +3451,67 @@
       <c r="M22" s="21" t="n">
         <v>0.5804004214963119</v>
       </c>
-      <c r="N22" s="27" t="n">
+      <c r="N22" s="21" t="n">
+        <v>0.6305495764948237</v>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>-0.0501491549985118</v>
+      </c>
+      <c r="P22" s="27" t="n">
         <v>370.8252559912854</v>
       </c>
-      <c r="O22" s="22" t="n">
+      <c r="Q22" s="22" t="n">
         <v>0.3600245203798887</v>
       </c>
-      <c r="P22" s="22" t="n">
+      <c r="R22" s="22" t="n">
         <v>0.2089583833774949</v>
       </c>
-      <c r="Q22" s="22" t="n">
+      <c r="S22" s="22" t="n">
         <v>0.1852280674779247</v>
       </c>
-      <c r="R22" s="22" t="n">
+      <c r="T22" s="22" t="n">
         <v>0.2270133088532909</v>
       </c>
-      <c r="S22" s="22" t="n">
+      <c r="U22" s="22" t="n">
         <v>-0.01805492547579593</v>
       </c>
-      <c r="T22" s="28" t="n">
+      <c r="V22" s="28" t="n">
         <v>2042505.51</v>
       </c>
-      <c r="U22" s="28" t="n">
+      <c r="W22" s="28" t="n">
         <v>1810548.791176471</v>
       </c>
-      <c r="V22" s="28" t="n">
+      <c r="X22" s="28" t="n">
         <v>231956.7188235293</v>
       </c>
-      <c r="W22" s="21" t="n">
+      <c r="Y22" s="21" t="n">
         <v>0.1135647946543504</v>
       </c>
-      <c r="X22" s="28" t="n">
+      <c r="Z22" s="28" t="n">
         <v>408438.1988717915</v>
       </c>
-      <c r="Y22" s="28" t="n">
+      <c r="AA22" s="28" t="n">
         <v>2218986.990048262</v>
       </c>
-      <c r="Z22" s="28" t="n">
+      <c r="AB22" s="28" t="n">
         <v>-176481.4800482623</v>
       </c>
-      <c r="AA22" s="23" t="inlineStr">
+      <c r="AC22" s="23" t="inlineStr">
         <is>
           <t>AJUSTAR</t>
         </is>
       </c>
-      <c r="AB22" s="19" t="inlineStr">
+      <c r="AD22" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC22" s="19" t="inlineStr">
+      <c r="AE22" s="19" t="inlineStr">
         <is>
           <t>cobre o variavel, nao o fixo rateado</t>
         </is>
       </c>
-      <c r="AD22" s="19" t="inlineStr">
+      <c r="AF22" s="19" t="inlineStr">
         <is>
           <t>ocupacao (rever frequencia e horario)</t>
         </is>
@@ -3399,61 +3567,67 @@
       <c r="M23" s="16" t="n">
         <v>0.5030077427039905</v>
       </c>
-      <c r="N23" s="24" t="n">
+      <c r="N23" s="16" t="n">
+        <v>0.6616411764710991</v>
+      </c>
+      <c r="O23" s="16" t="n">
+        <v>-0.1586334337671086</v>
+      </c>
+      <c r="P23" s="24" t="n">
         <v>91.45337872239655</v>
       </c>
-      <c r="O23" s="17" t="n">
+      <c r="Q23" s="17" t="n">
         <v>0.1555329570108785</v>
       </c>
-      <c r="P23" s="17" t="n">
+      <c r="R23" s="17" t="n">
         <v>0.07823428162211878</v>
       </c>
-      <c r="Q23" s="17" t="n">
+      <c r="S23" s="17" t="n">
         <v>0.07928926353149957</v>
       </c>
-      <c r="R23" s="17" t="n">
+      <c r="T23" s="17" t="n">
         <v>0.1029070086567065</v>
       </c>
-      <c r="S23" s="17" t="n">
+      <c r="U23" s="17" t="n">
         <v>-0.02467272703458773</v>
       </c>
-      <c r="T23" s="25" t="n">
+      <c r="V23" s="25" t="n">
         <v>1544739.02</v>
       </c>
-      <c r="U23" s="25" t="n">
+      <c r="W23" s="25" t="n">
         <v>1565569.68</v>
       </c>
-      <c r="V23" s="25" t="n">
+      <c r="X23" s="25" t="n">
         <v>-20830.66000000015</v>
       </c>
-      <c r="W23" s="16" t="n">
+      <c r="Y23" s="16" t="n">
         <v>-0.01348490568976509</v>
       </c>
-      <c r="X23" s="25" t="n">
+      <c r="Z23" s="25" t="n">
         <v>466333.3222070163</v>
       </c>
-      <c r="Y23" s="25" t="n">
+      <c r="AA23" s="25" t="n">
         <v>2031903.002207016</v>
       </c>
-      <c r="Z23" s="25" t="n">
+      <c r="AB23" s="25" t="n">
         <v>-487163.9822070161</v>
       </c>
-      <c r="AA23" s="18" t="inlineStr">
+      <c r="AC23" s="18" t="inlineStr">
         <is>
           <t>REVER</t>
         </is>
       </c>
-      <c r="AB23" s="14" t="inlineStr">
+      <c r="AD23" s="14" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC23" s="14" t="inlineStr">
+      <c r="AE23" s="14" t="inlineStr">
         <is>
           <t>receita nao cobre o custo variavel</t>
         </is>
       </c>
-      <c r="AD23" s="14" t="inlineStr">
+      <c r="AF23" s="14" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -3509,61 +3683,67 @@
       <c r="M24" s="21" t="n">
         <v>0.6157236450268017</v>
       </c>
-      <c r="N24" s="27" t="n">
+      <c r="N24" s="21" t="n">
+        <v>0.8190250439898525</v>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>-0.2033013989630509</v>
+      </c>
+      <c r="P24" s="27" t="n">
         <v>117.6607535306636</v>
       </c>
-      <c r="O24" s="22" t="n">
+      <c r="Q24" s="22" t="n">
         <v>0.1498863102301447</v>
       </c>
-      <c r="P24" s="22" t="n">
+      <c r="R24" s="22" t="n">
         <v>0.09228854527452268</v>
       </c>
-      <c r="Q24" s="22" t="n">
+      <c r="S24" s="22" t="n">
         <v>0.099142896704514</v>
       </c>
-      <c r="R24" s="22" t="n">
+      <c r="T24" s="22" t="n">
         <v>0.1227606418297209</v>
       </c>
-      <c r="S24" s="22" t="n">
+      <c r="U24" s="22" t="n">
         <v>-0.03047209655519827</v>
       </c>
-      <c r="T24" s="28" t="n">
+      <c r="V24" s="28" t="n">
         <v>1216376.87</v>
       </c>
-      <c r="U24" s="28" t="n">
+      <c r="W24" s="28" t="n">
         <v>1306718.25</v>
       </c>
-      <c r="V24" s="28" t="n">
+      <c r="X24" s="28" t="n">
         <v>-90341.38000000012</v>
       </c>
-      <c r="W24" s="21" t="n">
+      <c r="Y24" s="21" t="n">
         <v>-0.0742708795506775</v>
       </c>
-      <c r="X24" s="28" t="n">
+      <c r="Z24" s="28" t="n">
         <v>311285.4234119964</v>
       </c>
-      <c r="Y24" s="28" t="n">
+      <c r="AA24" s="28" t="n">
         <v>1618003.673411997</v>
       </c>
-      <c r="Z24" s="28" t="n">
+      <c r="AB24" s="28" t="n">
         <v>-401626.8034119965</v>
       </c>
-      <c r="AA24" s="18" t="inlineStr">
+      <c r="AC24" s="18" t="inlineStr">
         <is>
           <t>REVER</t>
         </is>
       </c>
-      <c r="AB24" s="19" t="inlineStr">
+      <c r="AD24" s="19" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="AC24" s="19" t="inlineStr">
+      <c r="AE24" s="19" t="inlineStr">
         <is>
           <t>receita nao cobre o custo variavel</t>
         </is>
       </c>
-      <c r="AD24" s="19" t="inlineStr">
+      <c r="AF24" s="19" t="inlineStr">
         <is>
           <t>ocupacao e preco</t>
         </is>
@@ -3597,53 +3777,59 @@
       <c r="M25" s="31" t="n">
         <v>0.6715615761944672</v>
       </c>
-      <c r="N25" s="32" t="n">
+      <c r="N25" s="31" t="n">
+        <v>0.5575790825251148</v>
+      </c>
+      <c r="O25" s="31" t="n">
+        <v>0.1139824936693524</v>
+      </c>
+      <c r="P25" s="32" t="n">
         <v>104.8627645825493</v>
       </c>
-      <c r="O25" s="33" t="n">
+      <c r="Q25" s="33" t="n">
         <v>0.223544735894332</v>
       </c>
-      <c r="P25" s="33" t="n">
+      <c r="R25" s="33" t="n">
         <v>0.1501240551871734</v>
       </c>
-      <c r="Q25" s="33" t="n">
+      <c r="S25" s="33" t="n">
         <v>0.09851978378168719</v>
       </c>
-      <c r="R25" s="33" t="n">
+      <c r="T25" s="33" t="n">
         <v>0.1246438687432807</v>
       </c>
-      <c r="S25" s="33" t="n">
+      <c r="U25" s="33" t="n">
         <v>0.02548018644389274</v>
       </c>
-      <c r="T25" s="34" t="n">
+      <c r="V25" s="34" t="n">
         <v>68269329.94</v>
       </c>
-      <c r="U25" s="34" t="n">
+      <c r="W25" s="34" t="n">
         <v>44802144.57452332</v>
       </c>
-      <c r="V25" s="34" t="n">
+      <c r="X25" s="34" t="n">
         <v>23467185.36547668</v>
       </c>
-      <c r="W25" s="31" t="n">
+      <c r="Y25" s="31" t="n">
         <v>0.3437441877062706</v>
       </c>
-      <c r="X25" s="34" t="n">
+      <c r="Z25" s="34" t="n">
         <v>11880000</v>
       </c>
-      <c r="Y25" s="34" t="n">
+      <c r="AA25" s="34" t="n">
         <v>56682144.57452332</v>
       </c>
-      <c r="Z25" s="34" t="n">
+      <c r="AB25" s="34" t="n">
         <v>11587185.36547668</v>
       </c>
-      <c r="AA25" s="29" t="n"/>
-      <c r="AB25" s="29" t="n"/>
       <c r="AC25" s="29" t="n"/>
       <c r="AD25" s="29" t="n"/>
+      <c r="AE25" s="29" t="n"/>
+      <c r="AF25" s="29" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AD24"/>
-  <conditionalFormatting sqref="W5:W24">
+  <autoFilter ref="A4:AF24"/>
+  <conditionalFormatting sqref="Y5:Y24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3655,7 +3841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S24">
+  <conditionalFormatting sqref="U5:U24">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3667,8 +3853,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O24">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M5:M24">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="4">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -49444,7 +49642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -49712,100 +49910,100 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Spread RASK-CASK</t>
+          <t>LF de equilibrio</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>RASK - CASK total</t>
+          <t>CASK total / yield</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>R$ por assento-km</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D15" s="38" t="inlineStr">
         <is>
-          <t>O resultado por assento oferecido. Positivo: a linha cobre o custo cheio. E o que classifica.</t>
+          <t>A ocupacao que a linha precisaria ter, ao yield que ja pratica, para empatar com o custo cheio. Sai da identidade RASK = yield x LF.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Folga de ocupacao</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>receita - custo total</t>
+          <t>load factor - LF de equilibrio</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>p.p.</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>O mesmo spread, em reais.</t>
+          <t>O mesmo que o spread, em unidade que a operacao entende: 'faltam 8 pontos de ocupacao' e acionavel, '-R$ 0,015 por assento-km' nao.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>Spread RASK-CASK</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>spread &gt;= 0</t>
+          <t>RASK - CASK total</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ por assento-km</t>
         </is>
       </c>
       <c r="D17" s="38" t="inlineStr">
         <is>
-          <t>Cobre o custo cheio. Acompanhar.</t>
+          <t>O resultado por assento oferecido. Positivo: a linha cobre o custo cheio. E o que classifica.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>AJUSTAR</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>MC &gt; 0 e spread &lt; 0</t>
+          <t>receita - custo total</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Contribui para o fixo mas nao o cobre. Mexer em frequencia, classe, horario ou preco — nao na existencia da linha.</t>
+          <t>O mesmo spread, em reais.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>MANTER</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>MC &lt;= 0</t>
+          <t>spread &gt;= 0</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -49815,27 +50013,71 @@
       </c>
       <c r="D19" s="38" t="inlineStr">
         <is>
-          <t>Nao cobre nem o variavel. Volume nao resolve: vender mais assento com MC negativa piora o resultado.</t>
+          <t>Cobre o custo cheio. Acompanhar.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>MC &gt; 0 e spread &lt; 0</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Contribui para o fixo mas nao o cobre. Mexer em frequencia, classe, horario ou preco — nao na existencia da linha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>MC &lt;= 0</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>Nao cobre nem o variavel. Volume nao resolve: vender mais assento com MC negativa piora o resultado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>No limite</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>|spread| &lt; R$ 0.010/ASK</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>Qualifica a classificacao: cobre o custo, mas uma alta de diesel reverte.</t>
         </is>

--- a/saida/margem-linhas-rodoviarias.xlsx
+++ b/saida/margem-linhas-rodoviarias.xlsx
@@ -48564,7 +48564,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rateio medio (R$/km rodado)</t>
+          <t>Rateio medio (R$ por km)</t>
         </is>
       </c>
       <c r="B17" s="37" t="n">

--- a/saida/margem-linhas-rodoviarias.xlsx
+++ b/saida/margem-linhas-rodoviarias.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Linhas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Mensal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Custos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dicionario" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Metodologia" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Estresse" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dicionario" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Metodologia" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumo'!$1:$1</definedName>
@@ -21,8 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mensal'!$A$4:$AB$484</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mensal'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Custos'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Dicionario'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Metodologia'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Estresse'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Dicionario'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Metodologia'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -140,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +183,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -49642,6 +49646,1694 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quanto a decisao aguenta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sensibilidade a cada premissa, preco de diesel de ruptura por linha, e a classificacao como probabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sensibilidade do resultado da rede</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Premissa</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Premissa -10%</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Premissa +10%</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>MANTER a -10%</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>MANTER a +10%</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Elasticidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Tarifa</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>-0.5891864870256307</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0.5891710794875296</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>-5.891787832565801</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Demanda</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>-0.5892445390873509</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0.5869576385878599</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>-5.881010888376053</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Diesel (R$/l)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.2066569394485405</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>-0.2066569394485412</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>2.066569394485408</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Bloco de custo fixo</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>0.1025270557541584</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>-0.1025270557541592</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" s="39" t="n">
+        <v>1.025270557541588</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Tripulacao (R$/h)</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>0.08296213011868447</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>-0.08296213011868547</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>0.8296213011868497</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Pneus e manutencao (R$/km)</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0.08262196450678849</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>-0.08262196450678938</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>0.8262196450678894</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Pedagio</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>0.01441148904871503</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>-0.01441148904871559</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>0.1441148904871531</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Preco do diesel em que cada linha deixa de cobrir</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Fator abaixo de 1: o diesel teria que CAIR para a linha cobrir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Linha</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Classificacao</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Fator de ruptura</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Diesel de ruptura</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>folga</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Situacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Curitiba PR</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>2.304096054288114</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>14.1701907338719</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>1.304096054288114</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Goiania GO - Brasilia DF</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>2.166187397254633</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>13.32205249311599</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>1.166187397254633</v>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Curitiba PR - Florianopolis SC</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="n">
+        <v>2.055491611734884</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>12.64127341216954</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>1.055491611734884</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Porto Alegre RS - Florianopolis SC</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>2.029914206618653</v>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>12.48397237070472</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>1.029914206618653</v>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Belo Horizonte MG</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>2.010748951298909</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>12.36610605048829</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>1.010748951298909</v>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Belo Horizonte MG - Rio de Janeiro RJ</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="n">
+        <v>1.778037437540201</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>10.93493024087223</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>0.7780374375402006</v>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Recife PE - Maceio AL</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>1.777432778870211</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>10.9312115900518</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>0.7774327788702113</v>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Rio de Janeiro RJ</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D23" s="39" t="n">
+        <v>1.710073438896104</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>10.51695164921104</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0.7100734388961039</v>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Salvador BA - Aracaju SE</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="n">
+        <v>1.617818396655004</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>9.949583139428274</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>0.6178183966550037</v>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Uberlandia MG - Sao Paulo SP</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="n">
+        <v>1.51938625238923</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>9.344225452193767</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>0.5193862523892303</v>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Natal RN - Fortaleza CE</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="n">
+        <v>1.302134285697677</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>8.008125857040717</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>0.3021342856976774</v>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Vitoria ES - Rio de Janeiro RJ</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="n">
+        <v>1.253221654566751</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>7.707313175585521</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>0.2532216545667514</v>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Campo Grande MS - Sao Paulo SP</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>LEITO</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D28" s="38" t="n">
+        <v>1.080473335681808</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>6.64491101444312</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>0.08047333568180814</v>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Campo Grande MS - Cuiaba MT</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="n">
+        <v>1.015672861245711</v>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>6.246388096661124</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>0.0156728612457111</v>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Brasilia DF - Belo Horizonte MG</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="n">
+        <v>0.8814016403611965</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>5.420620088221359</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>-0.1185983596388035</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Foz do Iguacu PR</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>LEITO</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D31" s="39" t="n">
+        <v>0.8053590960902003</v>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>4.952958440954732</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>-0.1946409039097997</v>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Cuiaba MT - Goiania GO</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="n">
+        <v>0.7397233589938553</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>4.54929865781221</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>-0.2602766410061447</v>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Belem PA - Sao Luis MA</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="n">
+        <v>0.714974291291947</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>4.397091891445474</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>-0.285025708708053</v>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Fortaleza CE - Teresina PI</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="n">
+        <v>0.4463680762970559</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>2.745163669226894</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>-0.5536319237029441</v>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Manaus AM - Boa Vista RR</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>nao cobre em toda a faixa varrida</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>A decisao como probabilidade</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>400 cenarios com as sete premissas sorteadas juntas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>Linha</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Decisao do relatorio</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Confianca no rotulo</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>Rotulo fragil</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Curitiba PR</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Goiania GO - Brasilia DF</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Porto Alegre RS - Florianopolis SC</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Belo Horizonte MG</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Curitiba PR - Florianopolis SC</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>Belo Horizonte MG - Rio de Janeiro RJ</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Recife PE - Maceio AL</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Rio de Janeiro RJ</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="21" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="H46" s="19" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Salvador BA - Aracaju SE</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>Uberlandia MG - Sao Paulo SP</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>0.9525</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>0.9525</v>
+      </c>
+      <c r="H48" s="19" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Natal RN - Fortaleza CE</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>Vitoria ES - Rio de Janeiro RJ</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>EXECUTIVO</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="21" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="H50" s="19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Campo Grande MS - Sao Paulo SP</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>LEITO</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>Campo Grande MS - Cuiaba MT</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>MANTER</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>0.5525</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="F52" s="21" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>0.5525</v>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Brasilia DF - Belo Horizonte MG</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP - Foz do Iguacu PR</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>LEITO</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="F54" s="21" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="H54" s="19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Cuiaba MT - Goiania GO</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>Belem PA - Sao Luis MA</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>SEMILEITO</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>AJUSTAR</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="F56" s="21" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H56" s="19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Fortaleza CE - Teresina PI</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>Manaus AM - Boa Vista RR</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G58" s="21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H58" s="19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Resultado da rede nos cenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Percentil 5</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>-894944.9235780394</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Mediana</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>11858547.51185317</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Percentil 95</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>24782308.24553946</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Probabilidade de prejuizo</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G39:G58">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -49703,7 +51395,7 @@
           <t>assento-km</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>A oferta. Denominador de RASK, CASK e load factor.</t>
         </is>
@@ -49725,7 +51417,7 @@
           <t>passageiro-km</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>A demanda transportada. Aqui todo passageiro viaja o trecho inteiro.</t>
         </is>
@@ -49747,7 +51439,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr">
         <is>
           <t>Quanto da oferta foi vendida. Teto do modelo: 96%.</t>
         </is>
@@ -49769,7 +51461,7 @@
           <t>R$</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>O bilhete medio. Sobe no pico, quando ha menos promocional.</t>
         </is>
@@ -49791,7 +51483,7 @@
           <t>R$ por pax-km</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>Preco por unidade de distancia vendida. Comparavel entre linhas de tamanhos diferentes, ao contrario da tarifa media.</t>
         </is>
@@ -49813,7 +51505,7 @@
           <t>R$ por assento-km</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>Receita por assento oferecido. Identidade: RASK = yield x load factor.</t>
         </is>
@@ -49835,7 +51527,7 @@
           <t>R$ por assento-km</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>Custo que so existe se o onibus sair.</t>
         </is>
@@ -49857,7 +51549,7 @@
           <t>R$ por assento-km</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>Custo cheio, com o pedaco de estrutura rateado por km rodado.</t>
         </is>
@@ -49879,7 +51571,7 @@
           <t>R$</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>Quanto a linha sobra para pagar o fixo. Negativa: cada partida destroi caixa.</t>
         </is>
@@ -49901,7 +51593,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>A margem em percentual da receita, comparavel entre linhas.</t>
         </is>
@@ -49923,7 +51615,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>A ocupacao que a linha precisaria ter, ao yield que ja pratica, para empatar com o custo cheio. Sai da identidade RASK = yield x LF.</t>
         </is>
@@ -49945,7 +51637,7 @@
           <t>p.p.</t>
         </is>
       </c>
-      <c r="D16" s="39" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>O mesmo que o spread, em unidade que a operacao entende: 'faltam 8 pontos de ocupacao' e acionavel, '-R$ 0,015 por assento-km' nao.</t>
         </is>
@@ -49967,7 +51659,7 @@
           <t>R$ por assento-km</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>O resultado por assento oferecido. Positivo: a linha cobre o custo cheio. E o que classifica.</t>
         </is>
@@ -49989,7 +51681,7 @@
           <t>R$</t>
         </is>
       </c>
-      <c r="D18" s="39" t="inlineStr">
+      <c r="D18" s="41" t="inlineStr">
         <is>
           <t>O mesmo spread, em reais.</t>
         </is>
@@ -50011,7 +51703,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>Cobre o custo cheio. Acompanhar.</t>
         </is>
@@ -50033,7 +51725,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr">
         <is>
           <t>Contribui para o fixo mas nao o cobre. Mexer em frequencia, classe, horario ou preco — nao na existencia da linha.</t>
         </is>
@@ -50055,7 +51747,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr">
+      <c r="D21" s="40" t="inlineStr">
         <is>
           <t>Nao cobre nem o variavel. Volume nao resolve: vender mais assento com MC negativa piora o resultado.</t>
         </is>
@@ -50077,7 +51769,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D22" s="39" t="inlineStr">
+      <c r="D22" s="41" t="inlineStr">
         <is>
           <t>Qualifica a classificacao: cobre o custo, mas uma alta de diesel reverte.</t>
         </is>
@@ -50089,7 +51781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -50124,14 +51816,14 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Um exercicio de analise de margem por linha de onibus interestadual. As cidades e as distancias sao reais; todos os numeros de operacao, demanda, tarifa e custo sao SINTETICOS, gerados por codigo a partir de premissas declaradas. Nada aqui vem de sistema, planilha ou base de empresa nenhuma.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Periodo: 2024-10 a 2026-09 (24 meses). Escopo: 20 linhas. Semente do gerador: 20260924 — a mesma execucao produz sempre os mesmos numeros.</t>
         </is>
@@ -50145,28 +51837,28 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>passageiros = ocupacao base x sazonalidade^amplitude x tendencia x ruido, cortado no teto de oferta.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>A sazonalidade e um indice mensal de media 1 (julho 1,22 e janeiro 1,18 no topo; marco 0,87 e maio 0,88 no fundo), elevado a um expoente proprio de cada linha: linha corporativa achata a curva (Goiania-Brasilia, 0,4), linha de lazer exagera (Sao Paulo-Foz, 1,6). Sazonalidade identica em todas as linhas e a assinatura mais obvia de dado inventado.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>O teto de ocupacao e 96%: nenhuma linha vende o mes inteiro, sobra assento no horario ruim e no dia de semana. Sem esse teto, o pico de julho produziria load factor acima de 100%.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>A tendencia e de 103% ao ano, centrada no meio do periodo, e o ruido e lognormal com desvio de 6% ao mes.</t>
         </is>
@@ -50180,14 +51872,14 @@
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>A tarifa parte de um valor de referencia em R$ por passageiro-km da classe (convencional 0,175 ate leito 0,400) e cai com a distancia pelo fator (500/km)^0,18 — o custo de terminal, embarque e venda se dilui em percurso maior, e por isso R$/km de uma linha de 200 km e naturalmente maior que o de um leito de 1.000 km.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Depois entra o fator de pressao competitiva da linha (0,92 em Sao Paulo-Rio, onde a aerea concorre; 1,02 em Sao Paulo-Foz, rota turistica com pouca alternativa direta) e a sensibilidade da tarifa ao mes: no pico sobra menos promocional e a tarifa media sobe.</t>
         </is>
@@ -50201,21 +51893,21 @@
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>Cinco componentes variaveis, com a base explicita. Por km: combustivel (diesel dividido pelo consumo da classe), pneus, manutencao (com fator de agressividade do corredor) e pedagio (R$/km do corredor). Por partida: tripulacao, que e jornada x custo-hora mais diaria e pernoite.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>Tripulacao por PARTIDA e nao por km e a decisao que mais muda o resultado. Acima de 600 km entra o segundo motorista e o custo de tripulacao por km quase dobra — uma linha de 610 km carrega quase o dobro de tripulacao por km de uma de 590 km, com receita por km parecida. E o degrau que explica boa parte das linhas classificadas como AJUSTAR.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>O fixo e um bloco mensal de R$ 990.000 (garagem, administracao e vendas, depreciacao e seguros), rateado pelos km rodados do mes. A soma do rateado fecha com o total declarado em cada mes.</t>
         </is>
@@ -50229,21 +51921,21 @@
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>A classificacao usa a janela dos 12 ultimos meses somados, nunca o mes isolado: uma linha de lazer cobre o custo cheio com folga em julho e nao cobre nem o variavel em maio, e decidir mes a mes faria a mesma linha alternar entre MANTER e REVER tres vezes ao ano.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="42" t="inlineStr">
         <is>
           <t>A escada tem dois degraus. MANTER cobre o custo cheio. AJUSTAR cobre o variavel mas nao o fixo rateado — e a linha CONTRIBUI: tirada da malha, o fixo que ela cobria se redistribui entre as outras e piora todas. REVER nao cobre nem o variavel, e ai volume nao resolve.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>A coluna Alavanca vem da identidade RASK = yield x load factor: se a linha nao cobre o custo, falta preco ou falta ocupacao, e as duas coisas pedem acao diferente. A comparacao e contra a mediana da rede.</t>
         </is>
@@ -50257,21 +51949,21 @@
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="42" t="inlineStr">
         <is>
           <t>Todo passageiro viaja o trecho inteiro, entao passageiro-km e simplesmente passageiros x km. Um modelo com secoes intermediarias exigiria a ocupacao trecho a trecho para ratear a capacidade, e sem isso qualquer 'ocupacao por secao' seria um rateio inventado.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr">
         <is>
           <t>A linha e medida em um sentido. Sentido de volta com ocupacao diferente (o classico vazio do retorno de feriado) nao esta modelado.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="42" t="inlineStr">
         <is>
           <t>O rateio do fixo por km e uma convencao, nao uma verdade: ele segue a intensidade de uso de frota e oficina, mas nenhuma decisao de cortar linha deve sair so dele. E por isso que a margem de contribuicao aparece sempre ao lado.</t>
         </is>
